--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484044_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484044_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.6972</v>
+        <v>7.909</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6549</v>
+        <v>4.8387</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0423</v>
+        <v>3.0704</v>
       </c>
       <c r="G2" t="n">
         <v>2.7044</v>
@@ -610,13 +610,13 @@
         <v>1.5871</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8496</v>
+        <v>1.0614</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3038</v>
+        <v>0.4876</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5458</v>
+        <v>0.5738</v>
       </c>
       <c r="V2" t="n">
         <v>3.5481</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.023300000000001</v>
+        <v>7.0653</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6798</v>
+        <v>3.7219</v>
       </c>
       <c r="F3" t="n">
         <v>3.3434</v>
@@ -688,10 +688,10 @@
         <v>2.3806</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8455</v>
+        <v>1.8875</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0463</v>
+        <v>1.0884</v>
       </c>
       <c r="U3" t="n">
         <v>0.7991</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3439</v>
+        <v>3.4147</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9106</v>
+        <v>1.581</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4333</v>
+        <v>1.8337</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6701</v>
+        <v>3.4256</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.6355</v>
+        <v>0.3629</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9654</v>
+        <v>3.0627</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1217</v>
+        <v>3.6668</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2865</v>
+        <v>1.6989</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4082</v>
+        <v>1.9679</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7918</v>
+        <v>-0.2412</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.3489</v>
+        <v>-1.336</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5572</v>
+        <v>1.0948</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7855</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7855</v>
+        <v>1.9838</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4945</v>
+        <v>1.5842</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7889</v>
+        <v>0.89</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7056</v>
+        <v>0.6943</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.266</v>
+        <v>-0.6032</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.266</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>P. RIOS CADENAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6967</v>
+        <v>3.3674</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6552</v>
+        <v>1.9239</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0414</v>
+        <v>1.4435</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1428</v>
+        <v>0.1982</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5907</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5521</v>
+        <v>0.732</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8908</v>
+        <v>0.9737</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1679</v>
+        <v>1.6087</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7229</v>
+        <v>-0.6349</v>
       </c>
       <c r="M5" t="n">
-        <v>1.252</v>
+        <v>-0.7755</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4228</v>
+        <v>-2.1424</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8292</v>
+        <v>1.3669</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5952</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3887</v>
+        <v>1.5871</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8874</v>
+        <v>1.5616</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7483</v>
+        <v>0.9296</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1392</v>
+        <v>0.6319</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.7384</v>
+        <v>2.0044</v>
       </c>
       <c r="W5" t="n">
+        <v>2.0044</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-1.7384</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.9482</v>
+        <v>3.2121</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9462</v>
+        <v>1.4512</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0021</v>
+        <v>1.7609</v>
       </c>
       <c r="G6" t="n">
-        <v>3.4256</v>
+        <v>4.1428</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3629</v>
+        <v>2.5907</v>
       </c>
       <c r="I6" t="n">
-        <v>3.0627</v>
+        <v>1.5521</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6668</v>
+        <v>2.8908</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6989</v>
+        <v>2.1679</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9679</v>
+        <v>0.7229</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2412</v>
+        <v>1.252</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.336</v>
+        <v>0.4228</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0948</v>
+        <v>0.8292</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9919</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9838</v>
+        <v>1.3887</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1177</v>
+        <v>1.4028</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2551</v>
+        <v>0.5442</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8626</v>
+        <v>0.8586</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6032</v>
+        <v>-1.7384</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6032</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. RIOS CADENAS</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4622</v>
+        <v>2.7979</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1871</v>
+        <v>2.5048</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2751</v>
+        <v>0.2931</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1982</v>
+        <v>-0.6701</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-2.6355</v>
       </c>
       <c r="I7" t="n">
-        <v>0.732</v>
+        <v>1.9654</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9737</v>
+        <v>1.1217</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6087</v>
+        <v>-0.2865</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6349</v>
+        <v>1.4082</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7755</v>
+        <v>-1.7918</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.1424</v>
+        <v>-2.3489</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3669</v>
+        <v>0.5572</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3968</v>
+        <v>1.7855</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6564</v>
+        <v>1.9485</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1928</v>
+        <v>1.3831</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4636</v>
+        <v>0.5653</v>
       </c>
       <c r="V7" t="n">
-        <v>2.0044</v>
+        <v>-0.266</v>
       </c>
       <c r="W7" t="n">
-        <v>2.0044</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0182</v>
+        <v>2.5332</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3847</v>
+        <v>2.8155</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3665</v>
+        <v>-0.2823</v>
       </c>
       <c r="G8" t="n">
         <v>1.4746</v>
@@ -1078,13 +1078,13 @@
         <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4246</v>
+        <v>0.9395</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1928</v>
+        <v>0.6236</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2318</v>
+        <v>0.316</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6745</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. VINÓS ALTEMIR</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.7942</v>
+        <v>2.3213</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1489</v>
+        <v>-0.0067</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6453</v>
+        <v>2.3281</v>
       </c>
       <c r="G9" t="n">
-        <v>3.0559</v>
+        <v>1.1505</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0134</v>
+        <v>-0.066</v>
       </c>
       <c r="I9" t="n">
-        <v>4.0693</v>
+        <v>1.2165</v>
       </c>
       <c r="J9" t="n">
-        <v>2.6939</v>
+        <v>-0.0295</v>
       </c>
       <c r="K9" t="n">
         <v>0.121</v>
       </c>
       <c r="L9" t="n">
-        <v>2.5729</v>
+        <v>-0.1504</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3621</v>
+        <v>1.1799</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1343</v>
+        <v>-0.187</v>
       </c>
       <c r="O9" t="n">
-        <v>1.4964</v>
+        <v>1.3669</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0.7935</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.07149999999999999</v>
+        <v>0.6433</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5611</v>
+        <v>0.0227</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4897</v>
+        <v>0.6206</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>V. VINÓS ALTEMIR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7551</v>
+        <v>2.2482</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5169</v>
+        <v>0.6591</v>
       </c>
       <c r="F10" t="n">
-        <v>2.272</v>
+        <v>1.5892</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1505</v>
+        <v>3.0559</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.066</v>
+        <v>-1.0134</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2165</v>
+        <v>4.0693</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0295</v>
+        <v>2.6939</v>
       </c>
       <c r="K10" t="n">
         <v>0.121</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1504</v>
+        <v>2.5729</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1799</v>
+        <v>0.3621</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.187</v>
+        <v>-1.1343</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3669</v>
+        <v>1.4964</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7935</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R10" t="n">
         <v>0.7935</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0771</v>
+        <v>0.3826</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4874</v>
+        <v>-0.051</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5645</v>
+        <v>0.4335</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6909</v>
+        <v>1.8031</v>
       </c>
       <c r="E11" t="n">
         <v>1.569</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1219</v>
+        <v>0.2341</v>
       </c>
       <c r="G11" t="n">
         <v>1.2743</v>
@@ -1312,13 +1312,13 @@
         <v>1.3887</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7664</v>
+        <v>0.8786</v>
       </c>
       <c r="T11" t="n">
         <v>0.3798</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3865</v>
+        <v>0.4988</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7384</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.814</v>
+        <v>-2.4329</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6965</v>
+        <v>-3.5118</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8825</v>
+        <v>1.0789</v>
       </c>
       <c r="G12" t="n">
         <v>-3.6453</v>
@@ -1390,13 +1390,13 @@
         <v>1.3887</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3509</v>
+        <v>1.0302</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7368</v>
+        <v>0.4479</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3859</v>
+        <v>0.5823</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2065</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>33.6159</v>
+        <v>34.2393</v>
       </c>
       <c r="E13" t="n">
-        <v>16.923</v>
+        <v>17.5466</v>
       </c>
       <c r="F13" t="n">
-        <v>16.6928</v>
+        <v>16.693</v>
       </c>
       <c r="G13" t="n">
         <v>16.368</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3032999999999999</v>
+        <v>0.3032999999999995</v>
       </c>
       <c r="I13" t="n">
         <v>16.0647</v>
@@ -1450,7 +1450,7 @@
         <v>6.4445</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6695999999999998</v>
+        <v>0.6696</v>
       </c>
       <c r="N13" t="n">
         <v>-8.9505</v>
@@ -1459,7 +1459,7 @@
         <v>9.620199999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>4.9596</v>
+        <v>4.959600000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-10.911</v>
@@ -1468,19 +1468,19 @@
         <v>15.8707</v>
       </c>
       <c r="S13" t="n">
-        <v>12.6968</v>
+        <v>13.3202</v>
       </c>
       <c r="T13" t="n">
-        <v>6.1225</v>
+        <v>6.7459</v>
       </c>
       <c r="U13" t="n">
-        <v>6.5743</v>
+        <v>6.5742</v>
       </c>
       <c r="V13" t="n">
         <v>-0.4084999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>6.013199999999999</v>
+        <v>6.0132</v>
       </c>
       <c r="X13" t="n">
         <v>-6.4217</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5475</v>
+        <v>0.862</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7708</v>
+        <v>0.6687</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2233</v>
+        <v>0.1933</v>
       </c>
       <c r="G14" t="n">
         <v>1.3029</v>
@@ -1546,13 +1546,13 @@
         <v>1.7855</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.23</v>
+        <v>-0.9154</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5044</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7256</v>
+        <v>-0.309</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1206</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.0655</v>
+        <v>-0.3989</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1999</v>
+        <v>0.1062</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8656</v>
+        <v>-0.5051</v>
       </c>
       <c r="G15" t="n">
         <v>1.4222</v>
@@ -1624,13 +1624,13 @@
         <v>1.3887</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.1686</v>
+        <v>-1.5021</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0599</v>
+        <v>-0.7538</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1088</v>
+        <v>-0.7483</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1206</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.7331</v>
+        <v>-0.7962</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.581</v>
+        <v>-0.1729</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1521</v>
+        <v>-0.6233</v>
       </c>
       <c r="G16" t="n">
         <v>-1.8553</v>
@@ -1702,13 +1702,13 @@
         <v>1.9838</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.6912</v>
+        <v>-1.7543</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3092</v>
+        <v>-0.9011</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.382</v>
+        <v>-0.8532</v>
       </c>
       <c r="V16" t="n">
         <v>2.2182</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.9626</v>
+        <v>-2.949</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4268</v>
+        <v>-1.3248</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5358</v>
+        <v>-1.6242</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1935</v>
@@ -1780,13 +1780,13 @@
         <v>0.1984</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9262</v>
+        <v>-0.9126</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6858</v>
+        <v>-0.5838</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2404</v>
+        <v>-0.3288</v>
       </c>
       <c r="V17" t="n">
         <v>-0.0494</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. FIGUERAS GÜELL</t>
+          <t>A. ROSA BEJARANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.0448</v>
+        <v>-3.3678</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7474</v>
+        <v>-0.0488</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2975</v>
+        <v>-3.3191</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.1497</v>
+        <v>-0.542</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7791</v>
+        <v>2.1267</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3706</v>
+        <v>-2.6688</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2317</v>
+        <v>1.8909</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.312</v>
+        <v>3.2513</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0803</v>
+        <v>-1.3604</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.918</v>
+        <v>-2.433</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4671</v>
+        <v>-1.1246</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4509</v>
+        <v>-1.3084</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3968</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1984</v>
+        <v>-1.9838</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2919</v>
+        <v>-1.2371</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3173</v>
+        <v>-0.7538</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0254</v>
+        <v>-0.4833</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.7952</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.5931</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ROSA BEJARANO</t>
+          <t>A. FIGUERAS GÜELL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4452</v>
+        <v>-3.4572</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3548</v>
+        <v>-1.1555</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.0904</v>
+        <v>-2.3017</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.542</v>
+        <v>-3.1497</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1267</v>
+        <v>-1.7791</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.6688</v>
+        <v>-1.3706</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8909</v>
+        <v>-0.2317</v>
       </c>
       <c r="K19" t="n">
-        <v>3.2513</v>
+        <v>-0.312</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3604</v>
+        <v>0.0803</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.433</v>
+        <v>-2.918</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1246</v>
+        <v>-1.4671</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3084</v>
+        <v>-1.4509</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7935</v>
+        <v>0.3968</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9838</v>
+        <v>-0.1984</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3145</v>
+        <v>-0.7043</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0599</v>
+        <v>-0.7254</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2546</v>
+        <v>0.0212</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7952</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7979000000000001</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5931</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. GARCIA MARTINEZ</t>
+          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.9714</v>
+        <v>-4.0699</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9475</v>
+        <v>-2.0923</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.024</v>
+        <v>-1.9776</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.004</v>
+        <v>-3.7516</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9276</v>
+        <v>-3.2957</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0764</v>
+        <v>-0.4559</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4989</v>
+        <v>-1.2466</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5391</v>
+        <v>-1.9695</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0402</v>
+        <v>0.7229</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5051</v>
+        <v>-2.505</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3886</v>
+        <v>-1.3262</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1165</v>
+        <v>-1.1788</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3806</v>
+        <v>-1.5871</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3968</v>
+        <v>1.5871</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7176</v>
+        <v>-1.1875</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0679</v>
+        <v>-0.7311</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6497000000000001</v>
+        <v>-0.4564</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.266</v>
+        <v>0.8692</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.266</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
+          <t>A. GARCIA MARTINEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0478</v>
+        <v>-4.1976</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9903</v>
+        <v>-3.2535</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0575</v>
+        <v>-0.944</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.7516</v>
+        <v>-1.004</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.2957</v>
+        <v>-0.9276</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4559</v>
+        <v>-0.0764</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2466</v>
+        <v>-0.4989</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.9695</v>
+        <v>-0.5391</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7229</v>
+        <v>0.0402</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.505</v>
+        <v>-0.5051</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3262</v>
+        <v>-0.3886</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1788</v>
+        <v>-0.1165</v>
       </c>
       <c r="P21" t="n">
+        <v>-1.9838</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-2.3806</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.9438</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.374</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.5697</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.266</v>
+      </c>
+      <c r="W21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-1.5871</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.5871</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-1.1654</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-0.6291</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-0.5363</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0.8692</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.4724</v>
-      </c>
       <c r="X21" t="n">
-        <v>-0.6032</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.0689</v>
+        <v>-4.8207</v>
       </c>
       <c r="E22" t="n">
         <v>-4.1398</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9291</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-4.0935</v>
@@ -2170,13 +2170,13 @@
         <v>0.3968</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0531</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="T22" t="n">
         <v>-0.6235000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4297</v>
+        <v>-0.1814</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1206</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.8239</v>
+        <v>-9.0603</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0762</v>
+        <v>-5.2803</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.7477</v>
+        <v>-3.78</v>
       </c>
       <c r="G23" t="n">
         <v>-3.5035</v>
@@ -2248,13 +2248,13 @@
         <v>1.3887</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1382</v>
+        <v>-1.3745</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3173</v>
+        <v>-0.5214</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8209</v>
+        <v>-0.8532</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2065</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-33.6157</v>
+        <v>-32.2556</v>
       </c>
       <c r="E24" t="n">
-        <v>-16.6929</v>
+        <v>-16.693</v>
       </c>
       <c r="F24" t="n">
-        <v>-16.923</v>
+        <v>-15.5626</v>
       </c>
       <c r="G24" t="n">
         <v>-16.368</v>
@@ -2326,13 +2326,13 @@
         <v>10.9113</v>
       </c>
       <c r="S24" t="n">
-        <v>-12.6967</v>
+        <v>-11.3365</v>
       </c>
       <c r="T24" t="n">
         <v>-6.5743</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.1226</v>
+        <v>-4.7621</v>
       </c>
       <c r="V24" t="n">
         <v>0.4084999999999999</v>
